--- a/hr_interview_responses.xlsx
+++ b/hr_interview_responses.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Stay Interviews" sheetId="1" r:id="rId1"/>
+    <sheet name="90-Day Check-Ins" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +398,467 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Session ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Interview Type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Department</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Started At</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Saved At</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Q1</v>
+      </c>
+      <c r="I1" t="str">
+        <v>A1</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Q2</v>
+      </c>
+      <c r="K1" t="str">
+        <v>A2</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Q3</v>
+      </c>
+      <c r="M1" t="str">
+        <v>A3</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Q4</v>
+      </c>
+      <c r="O1" t="str">
+        <v>A4</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Q5</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>A5</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Q6</v>
+      </c>
+      <c r="S1" t="str">
+        <v>A6</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Q7</v>
+      </c>
+      <c r="U1" t="str">
+        <v>A7</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Q8</v>
+      </c>
+      <c r="W1" t="str">
+        <v>A8</v>
+      </c>
+      <c r="X1" t="str">
+        <v>Q9</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>A9</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>Q10</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>A10</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>Q11</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>A11</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>6fec9279-fc39-4a43-8513-600adbc559b0</v>
+      </c>
+      <c r="B2" t="str">
+        <v>stay</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Academic Affairs</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Less than 6 months</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-04-25T03:58:11.621Z</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-04-25T04:01:00.912Z</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
+      </c>
+      <c r="I2" t="str">
+        <v>I love that in being a CA i get to connect to all my residents and community on campus</v>
+      </c>
+      <c r="J2" t="str">
+        <v>That sense of community connection really comes through. What is it about those relationships that makes you want to stay at UW Oshkosh?</v>
+      </c>
+      <c r="K2" t="str">
+        <v>it just is building me up into a better person and i just get connected to more people</v>
+      </c>
+      <c r="L2" t="str">
+        <v>That's meaningful. How would you say your supervisor supports that growth you're experiencing?</v>
+      </c>
+      <c r="M2" t="str">
+        <v>they very much support everything i do, but sometimes i get back handed comments fro mthem</v>
+      </c>
+      <c r="N2" t="str">
+        <v>I hear that — support overall, but those occasional comments land differently. Can you give me a quick example of what that feels like?</v>
+      </c>
+      <c r="O2" t="str">
+        <v>it just doesnt feel good at all and makes me reconsider my role</v>
+      </c>
+      <c r="P2" t="str">
+        <v>That's important feedback. Beyond those moments, what would help you feel more valued and appreciated in your position?</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>i need to end this interview.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>609bd498-ec04-41aa-93ad-664a04012193</v>
+      </c>
+      <c r="B3" t="str">
+        <v>stay</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Academic Affairs</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Less than 6 months</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-04-25T04:16:26.967Z</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-04-25T04:27:43.965Z</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Complete</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
+      </c>
+      <c r="I3" t="str">
+        <v>i really love the community building aspects</v>
+      </c>
+      <c r="J3" t="str">
+        <v>That's meaningful — community building is something that really does define the experience here, and it sounds like that's at the heart of what energizes you. Can you tell me more about what community building looks like in your day-to-day work, or is there a specific project or interaction that stands out as an example?</v>
+      </c>
+      <c r="K3" t="str">
+        <v>i really love doing programs and meeting residents that way</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Programs are such a direct way to connect with people and see the impact you're making — it makes sense that face-to-face interaction would be fulfilling. When you're running these programs and meeting residents, what's the part that keeps you coming back? Is it the relationships themselves, watching people engage, or something else?</v>
+      </c>
+      <c r="M3" t="str">
+        <v>it is 100% the relationships ive maid</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Those genuine relationships you've built really do sound like they're the foundation of why you show up — that's powerful. I'm curious: beyond the programs themselves, do you feel like UW Oshkosh as an organization supports and values that relationship-building work you're doing, or is there anything that could make that aspect of your role even better?</v>
+      </c>
+      <c r="O3" t="str">
+        <v>i mean in my department yes i couldnt say for others</v>
+      </c>
+      <c r="P3" t="str">
+        <v>It's really telling that your department gets it and supports that work — that kind of alignment between what you care about and what your team values makes a difference. Since your department is doing well in that regard, I'm wondering: what does your supervisor or team do specifically that makes you feel supported in building those relationships?</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>well we all communicate well adn help eachother when needed</v>
+      </c>
+      <c r="R3" t="str">
+        <v>That collaborative spirit — where people actually step up for each other — creates a really different day-to-day experience. Beyond the teamwork itself, do you feel like your efforts and contributions are recognized by your supervisor or team, or is that something you'd like to see more of?</v>
+      </c>
+      <c r="S3" t="str">
+        <v>i mean no not really. i wish they were more</v>
+      </c>
+      <c r="T3" t="str">
+        <v>That's honest feedback, and it matters — doing meaningful work and not feeling like it's acknowledged can wear on people over time, even when the work itself is fulfilling. What would recognition look like for you? Are we talking about verbal appreciation, something more formal, or a different kind of acknowledgment altogether?</v>
+      </c>
+      <c r="U3" t="str">
+        <v>i would like verbal appreciation</v>
+      </c>
+      <c r="V3" t="str">
+        <v>Verbal appreciation — simple and direct, but it genuinely does land differently when someone takes the moment to actually say it. Have you had a chance to mention this to your supervisor, or does that feel like something you'd want to explore with them on your own, or would it help to have some support navigating that conversation?</v>
+      </c>
+      <c r="W3" t="str">
+        <v>no that is a conversation i wouldnt be able to navigate myself</v>
+      </c>
+      <c r="X3" t="str">
+        <v>I hear you — sometimes those conversations feel risky to initiate on your own, especially when you're not sure how it'll land. This might be a good moment to mention that our HR team can absolutely help you think through how to approach that conversation with your supervisor, or even facilitate it if that would feel more comfortable. Would it be helpful to connect with someone from HR about this?</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>yes thank you</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>I'm glad that feels like a helpful option — we'll make sure you get connected with someone who can support you through that. In the meantime, beyond recognition, is there anything else about your day-to-day experience or your role that you'd like to see change or improve?</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>no not really</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>That's great to hear — it sounds like aside from wanting to feel more verbally appreciated, you're in a pretty good place. Before we wrap up, I'm curious: what do you think would make you want to stay at UW Oshkosh for the long haul, or are you already feeling that commitment?</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>honestly just contiunieing to make connections keeps me going</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>7cebf88e-7395-4c79-bb2f-13001e0d892b</v>
+      </c>
+      <c r="B4" t="str">
+        <v>stay</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Academic Affairs</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Less than 6 months</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2026-04-25T04:28:41.336Z</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-04-25T04:32:35.874Z</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
+      </c>
+      <c r="I4" t="str">
+        <v>i really like the people but somoene has been trating me badly</v>
+      </c>
+      <c r="J4" t="str">
+        <v>I'm glad you feel connected to your colleagues — that sense of community really matters. I'm sorry to hear that someone's been treating you poorly; that's something we absolutely want to understand better. Can you tell me a bit about what's been happening?</v>
+      </c>
+      <c r="K4" t="str">
+        <v>i just feel like i need to speak to someone in HR</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>425ad6ee-8c8f-44d8-9b06-57e055c58457</v>
+      </c>
+      <c r="B5" t="str">
+        <v>stay</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Academic Affairs</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Less than 6 months</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-04-25T04:32:41.438Z</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-04-25T04:34:17.245Z</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
+      </c>
+      <c r="I5" t="str">
+        <v>i would like to schedule an interview with an hr rep</v>
+      </c>
+      <c r="J5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Of free coarse! I can definitely help connect you with someone from our HR team. Before we wrap up, would you still like to spend just a few minutes sharing what's on your mind, or would you prefer to save everything for your conversation with HR?
+Either way, I'll make sure to get your contact information and have someone reach out to schedule that meeting with you.</v>
+      </c>
+      <c r="K5" t="str">
+        <v>no it just is pertinent that i get in contact with someone</v>
+      </c>
+      <c r="L5" t="str" xml:space="preserve">
+        <v xml:space="preserve">I completely understand — I appreciate you letting me know what's most important right now. Let me make sure we get you connected with the right person on our HR team.
+Could you share your name and the best contact information (phone or email) where HR should reach out to you?</v>
+      </c>
+      <c r="M5" t="str">
+        <v>no can you direct me to them</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>b47b1728-1228-4f50-bafd-600c2ddb89d4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>stay</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Academic Affairs</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Less than 6 months</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2026-04-25T04:15:25.266Z</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-04-25T04:38:58.960Z</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Partial</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>0e1a34f3-ccd7-4b45-942c-ebedb0ce9556</v>
+      </c>
+      <c r="B7" t="str">
+        <v>stay</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Academic Affairs</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Less than 6 months</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2026-04-25T18:28:44.361Z</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-04-25T19:38:33.402Z</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
+      </c>
+      <c r="I7" t="str">
+        <v>I love he community building</v>
+      </c>
+      <c r="J7" t="str">
+        <v>That's really meaningful — community building is at the heart of what makes a workplace feel like more than just a job. Can you tell me a little more about what that looks like for you day-to-day, or a specific example of community building you've been part of recently?</v>
+      </c>
+      <c r="K7" t="str">
+        <v>yeah someone said something not nice to me</v>
+      </c>
+      <c r="L7" t="str">
+        <v>I'm sorry to hear that happened — that can be tough, especially when you're someone who values connection and community. How did you handle it, and has it affected how you're feeling about your role or your team since then?</v>
+      </c>
+      <c r="M7" t="str">
+        <v>yeah they called me a slur</v>
+      </c>
+      <c r="N7" t="str">
+        <v>I'm really sorry you experienced that — that's completely unacceptable, and I appreciate you sharing it with me. That kind of behavior has no place here at UW Oshkosh, and I want to make sure you get the support you deserve. Have you had a chance to report this to your supervisor or HR, and is there anything you need right now to feel safe and supported at work?</v>
+      </c>
+      <c r="O7" t="str">
+        <v>no I havent</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>24bc5cd6-1b0d-4f49-99ca-cd1f63337576</v>
+      </c>
+      <c r="B8" t="str">
+        <v>stay</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Academic Affairs</v>
+      </c>
+      <c r="D8" t="str">
+        <v>6–12 months</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2026-04-25T19:39:05.806Z</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-04-25T19:48:22.781Z</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
+      </c>
+      <c r="I8" t="str">
+        <v>I love the community and the people surrounding me</v>
+      </c>
+      <c r="J8" t="str">
+        <v>That's really meaningful — it sounds like the relationships and sense of belonging you've built here are a real anchor for you. When you think about the people around you, is that mostly your immediate team, or does it extend across the campus community more broadly?</v>
+      </c>
+      <c r="K8" t="str">
+        <v>I have had someone calling me slurs</v>
+      </c>
+      <c r="L8" t="str">
+        <v>I'm genuinely sorry to hear that's been happening — that's not okay, and I appreciate you sharing something so important with me. That kind of experience directly conflicts with the welcoming community you just described valuing so much. Can you tell me a bit more about what's been going on — who this person is, and whether you've had a chance to report it yet?</v>
+      </c>
+      <c r="M8" t="str">
+        <v>I haven't reported It yet</v>
+      </c>
+      <c r="N8" t="str">
+        <v>I hear you, and I'm glad you felt comfortable telling me about it now. Reporting something like this can feel daunting, but you absolutely deserve support and a safe workplace — that's non-negotiable here. Would you be comfortable speaking with someone in HR to discuss what's happened and explore your options? I can connect you directly, or we can talk through how that process works if that would help.</v>
+      </c>
+      <c r="O8" t="str">
+        <v>yes I would be comftorable</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>425d538e-cd61-46f3-a716-805ae954c8fa</v>
+      </c>
+      <c r="B9" t="str">
+        <v>stay</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Academic Affairs</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Less than 6 months</v>
+      </c>
+      <c r="E9" t="str">
+        <v>2026-04-30T00:05:36.752Z</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-04-30T22:25:39.658Z</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Partial</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
   <cols>
     <col min="1" max="1" width="36.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -454,79 +915,13 @@
       <c r="G1" t="str">
         <v>Status</v>
       </c>
-      <c r="H1" t="str">
-        <v>Q1</v>
-      </c>
-      <c r="I1" t="str">
-        <v>A1</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Q2</v>
-      </c>
-      <c r="K1" t="str">
-        <v>A2</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Q3</v>
-      </c>
-      <c r="M1" t="str">
-        <v>A3</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Q4</v>
-      </c>
-      <c r="O1" t="str">
-        <v>A4</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Q5</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>A5</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Q6</v>
-      </c>
-      <c r="S1" t="str">
-        <v>A6</v>
-      </c>
-      <c r="T1" t="str">
-        <v>Q7</v>
-      </c>
-      <c r="U1" t="str">
-        <v>A7</v>
-      </c>
-      <c r="V1" t="str">
-        <v>Q8</v>
-      </c>
-      <c r="W1" t="str">
-        <v>A8</v>
-      </c>
-      <c r="X1" t="str">
-        <v>Q9</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>A9</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>Q10</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>A10</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>Q11</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>A11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>6fec9279-fc39-4a43-8513-600adbc559b0</v>
+        <v>7b4ec95f-42ef-4286-ae62-0d55fdfa75c1</v>
       </c>
       <c r="B2" t="str">
-        <v>stay</v>
+        <v>ninety_day</v>
       </c>
       <c r="C2" t="str">
         <v>Academic Affairs</v>
@@ -535,332 +930,18 @@
         <v>Less than 6 months</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-04-25T03:58:11.621Z</v>
+        <v>2026-05-01T16:06:10.583Z</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-04-25T04:01:00.912Z</v>
+        <v>2026-05-02T02:51:49.358Z</v>
       </c>
       <c r="G2" t="str">
         <v>Partial</v>
       </c>
-      <c r="H2" t="str">
-        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
-      </c>
-      <c r="I2" t="str">
-        <v>I love that in being a CA i get to connect to all my residents and community on campus</v>
-      </c>
-      <c r="J2" t="str">
-        <v>That sense of community connection really comes through. What is it about those relationships that makes you want to stay at UW Oshkosh?</v>
-      </c>
-      <c r="K2" t="str">
-        <v>it just is building me up into a better person and i just get connected to more people</v>
-      </c>
-      <c r="L2" t="str">
-        <v>That's meaningful. How would you say your supervisor supports that growth you're experiencing?</v>
-      </c>
-      <c r="M2" t="str">
-        <v>they very much support everything i do, but sometimes i get back handed comments fro mthem</v>
-      </c>
-      <c r="N2" t="str">
-        <v>I hear that — support overall, but those occasional comments land differently. Can you give me a quick example of what that feels like?</v>
-      </c>
-      <c r="O2" t="str">
-        <v>it just doesnt feel good at all and makes me reconsider my role</v>
-      </c>
-      <c r="P2" t="str">
-        <v>That's important feedback. Beyond those moments, what would help you feel more valued and appreciated in your position?</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>i need to end this interview.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>609bd498-ec04-41aa-93ad-664a04012193</v>
-      </c>
-      <c r="B3" t="str">
-        <v>stay</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Academic Affairs</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Less than 6 months</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-04-25T04:16:26.967Z</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2026-04-25T04:27:43.965Z</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Complete</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
-      </c>
-      <c r="I3" t="str">
-        <v>i really love the community building aspects</v>
-      </c>
-      <c r="J3" t="str">
-        <v>That's meaningful — community building is something that really does define the experience here, and it sounds like that's at the heart of what energizes you. Can you tell me more about what community building looks like in your day-to-day work, or is there a specific project or interaction that stands out as an example?</v>
-      </c>
-      <c r="K3" t="str">
-        <v>i really love doing programs and meeting residents that way</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Programs are such a direct way to connect with people and see the impact you're making — it makes sense that face-to-face interaction would be fulfilling. When you're running these programs and meeting residents, what's the part that keeps you coming back? Is it the relationships themselves, watching people engage, or something else?</v>
-      </c>
-      <c r="M3" t="str">
-        <v>it is 100% the relationships ive maid</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Those genuine relationships you've built really do sound like they're the foundation of why you show up — that's powerful. I'm curious: beyond the programs themselves, do you feel like UW Oshkosh as an organization supports and values that relationship-building work you're doing, or is there anything that could make that aspect of your role even better?</v>
-      </c>
-      <c r="O3" t="str">
-        <v>i mean in my department yes i couldnt say for others</v>
-      </c>
-      <c r="P3" t="str">
-        <v>It's really telling that your department gets it and supports that work — that kind of alignment between what you care about and what your team values makes a difference. Since your department is doing well in that regard, I'm wondering: what does your supervisor or team do specifically that makes you feel supported in building those relationships?</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>well we all communicate well adn help eachother when needed</v>
-      </c>
-      <c r="R3" t="str">
-        <v>That collaborative spirit — where people actually step up for each other — creates a really different day-to-day experience. Beyond the teamwork itself, do you feel like your efforts and contributions are recognized by your supervisor or team, or is that something you'd like to see more of?</v>
-      </c>
-      <c r="S3" t="str">
-        <v>i mean no not really. i wish they were more</v>
-      </c>
-      <c r="T3" t="str">
-        <v>That's honest feedback, and it matters — doing meaningful work and not feeling like it's acknowledged can wear on people over time, even when the work itself is fulfilling. What would recognition look like for you? Are we talking about verbal appreciation, something more formal, or a different kind of acknowledgment altogether?</v>
-      </c>
-      <c r="U3" t="str">
-        <v>i would like verbal appreciation</v>
-      </c>
-      <c r="V3" t="str">
-        <v>Verbal appreciation — simple and direct, but it genuinely does land differently when someone takes the moment to actually say it. Have you had a chance to mention this to your supervisor, or does that feel like something you'd want to explore with them on your own, or would it help to have some support navigating that conversation?</v>
-      </c>
-      <c r="W3" t="str">
-        <v>no that is a conversation i wouldnt be able to navigate myself</v>
-      </c>
-      <c r="X3" t="str">
-        <v>I hear you — sometimes those conversations feel risky to initiate on your own, especially when you're not sure how it'll land. This might be a good moment to mention that our HR team can absolutely help you think through how to approach that conversation with your supervisor, or even facilitate it if that would feel more comfortable. Would it be helpful to connect with someone from HR about this?</v>
-      </c>
-      <c r="Y3" t="str">
-        <v>yes thank you</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>I'm glad that feels like a helpful option — we'll make sure you get connected with someone who can support you through that. In the meantime, beyond recognition, is there anything else about your day-to-day experience or your role that you'd like to see change or improve?</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>no not really</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>That's great to hear — it sounds like aside from wanting to feel more verbally appreciated, you're in a pretty good place. Before we wrap up, I'm curious: what do you think would make you want to stay at UW Oshkosh for the long haul, or are you already feeling that commitment?</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>honestly just contiunieing to make connections keeps me going</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>7cebf88e-7395-4c79-bb2f-13001e0d892b</v>
-      </c>
-      <c r="B4" t="str">
-        <v>stay</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Academic Affairs</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Less than 6 months</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2026-04-25T04:28:41.336Z</v>
-      </c>
-      <c r="F4" t="str">
-        <v>2026-04-25T04:32:35.874Z</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
-      </c>
-      <c r="I4" t="str">
-        <v>i really like the people but somoene has been trating me badly</v>
-      </c>
-      <c r="J4" t="str">
-        <v>I'm glad you feel connected to your colleagues — that sense of community really matters. I'm sorry to hear that someone's been treating you poorly; that's something we absolutely want to understand better. Can you tell me a bit about what's been happening?</v>
-      </c>
-      <c r="K4" t="str">
-        <v>i just feel like i need to speak to someone in HR</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str">
-        <v>425ad6ee-8c8f-44d8-9b06-57e055c58457</v>
-      </c>
-      <c r="B5" t="str">
-        <v>stay</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Academic Affairs</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Less than 6 months</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-04-25T04:32:41.438Z</v>
-      </c>
-      <c r="F5" t="str">
-        <v>2026-04-25T04:34:17.245Z</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
-      </c>
-      <c r="I5" t="str">
-        <v>i would like to schedule an interview with an hr rep</v>
-      </c>
-      <c r="J5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Of free coarse! I can definitely help connect you with someone from our HR team. Before we wrap up, would you still like to spend just a few minutes sharing what's on your mind, or would you prefer to save everything for your conversation with HR?
-Either way, I'll make sure to get your contact information and have someone reach out to schedule that meeting with you.</v>
-      </c>
-      <c r="K5" t="str">
-        <v>no it just is pertinent that i get in contact with someone</v>
-      </c>
-      <c r="L5" t="str" xml:space="preserve">
-        <v xml:space="preserve">I completely understand — I appreciate you letting me know what's most important right now. Let me make sure we get you connected with the right person on our HR team.
-Could you share your name and the best contact information (phone or email) where HR should reach out to you?</v>
-      </c>
-      <c r="M5" t="str">
-        <v>no can you direct me to them</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>b47b1728-1228-4f50-bafd-600c2ddb89d4</v>
-      </c>
-      <c r="B6" t="str">
-        <v>stay</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Academic Affairs</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Less than 6 months</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2026-04-25T04:15:25.266Z</v>
-      </c>
-      <c r="F6" t="str">
-        <v>2026-04-25T04:38:58.960Z</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Partial</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>0e1a34f3-ccd7-4b45-942c-ebedb0ce9556</v>
-      </c>
-      <c r="B7" t="str">
-        <v>stay</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Academic Affairs</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Less than 6 months</v>
-      </c>
-      <c r="E7" t="str">
-        <v>2026-04-25T18:28:44.361Z</v>
-      </c>
-      <c r="F7" t="str">
-        <v>2026-04-25T19:38:33.402Z</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
-      </c>
-      <c r="I7" t="str">
-        <v>I love he community building</v>
-      </c>
-      <c r="J7" t="str">
-        <v>That's really meaningful — community building is at the heart of what makes a workplace feel like more than just a job. Can you tell me a little more about what that looks like for you day-to-day, or a specific example of community building you've been part of recently?</v>
-      </c>
-      <c r="K7" t="str">
-        <v>yeah someone said something not nice to me</v>
-      </c>
-      <c r="L7" t="str">
-        <v>I'm sorry to hear that happened — that can be tough, especially when you're someone who values connection and community. How did you handle it, and has it affected how you're feeling about your role or your team since then?</v>
-      </c>
-      <c r="M7" t="str">
-        <v>yeah they called me a slur</v>
-      </c>
-      <c r="N7" t="str">
-        <v>I'm really sorry you experienced that — that's completely unacceptable, and I appreciate you sharing it with me. That kind of behavior has no place here at UW Oshkosh, and I want to make sure you get the support you deserve. Have you had a chance to report this to your supervisor or HR, and is there anything you need right now to feel safe and supported at work?</v>
-      </c>
-      <c r="O7" t="str">
-        <v>no I havent</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>24bc5cd6-1b0d-4f49-99ca-cd1f63337576</v>
-      </c>
-      <c r="B8" t="str">
-        <v>stay</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Academic Affairs</v>
-      </c>
-      <c r="D8" t="str">
-        <v>6–12 months</v>
-      </c>
-      <c r="E8" t="str">
-        <v>2026-04-25T19:39:05.806Z</v>
-      </c>
-      <c r="F8" t="str">
-        <v>2026-04-25T19:48:22.781Z</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Thank you for taking the time to participate in this stay interview. Your feedback helps UW Oshkosh continue to be a great place to work. Let's start with something positive — what do you enjoy most about your current role here?</v>
-      </c>
-      <c r="I8" t="str">
-        <v>I love the community and the people surrounding me</v>
-      </c>
-      <c r="J8" t="str">
-        <v>That's really meaningful — it sounds like the relationships and sense of belonging you've built here are a real anchor for you. When you think about the people around you, is that mostly your immediate team, or does it extend across the campus community more broadly?</v>
-      </c>
-      <c r="K8" t="str">
-        <v>I have had someone calling me slurs</v>
-      </c>
-      <c r="L8" t="str">
-        <v>I'm genuinely sorry to hear that's been happening — that's not okay, and I appreciate you sharing something so important with me. That kind of experience directly conflicts with the welcoming community you just described valuing so much. Can you tell me a bit more about what's been going on — who this person is, and whether you've had a chance to report it yet?</v>
-      </c>
-      <c r="M8" t="str">
-        <v>I haven't reported It yet</v>
-      </c>
-      <c r="N8" t="str">
-        <v>I hear you, and I'm glad you felt comfortable telling me about it now. Reporting something like this can feel daunting, but you absolutely deserve support and a safe workplace — that's non-negotiable here. Would you be comfortable speaking with someone in HR to discuss what's happened and explore your options? I can connect you directly, or we can talk through how that process works if that would help.</v>
-      </c>
-      <c r="O8" t="str">
-        <v>yes I would be comftorable</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>